--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033111</t>
+          <t xml:space="preserve">200033151</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -9964,7 +9964,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035229</t>
+          <t xml:space="preserve">200035250</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878988</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878984</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878986</t>
+          <t xml:space="preserve">311878990</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">

--- a/public/exports/26696348.xlsx
+++ b/public/exports/26696348.xlsx
@@ -9064,7 +9064,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033151</t>
+          <t xml:space="preserve">200033111</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035250</t>
+          <t xml:space="preserve">200035229</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878988</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878984</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878990</t>
+          <t xml:space="preserve">311878986</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
